--- a/tame_output/ON/bt/strategyON_20231122.xlsx
+++ b/tame_output/ON/bt/strategyON_20231122.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-21</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>88.3%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-21</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>21.6%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.4%</t>
+          <t>453.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>13.8%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>103.5%</t>
+          <t>102.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>98.8%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>27.1%</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>8.5%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>133.4%</t>
+          <t>132.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-11-21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>127.3%</t>
+          <t>125.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.6%</t>
+          <t>-14.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>26.7%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1788"/>
+  <dimension ref="A1:G1789"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.148611740249846</v>
+        <v>3.14673011872803</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -42650,6 +42650,29 @@
       </c>
       <c r="G1788" t="n">
         <v>4.406068928040899</v>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="A1789" s="2" t="n">
+        <v>45251</v>
+      </c>
+      <c r="B1789" t="n">
+        <v>3.118537813782241</v>
+      </c>
+      <c r="C1789" t="n">
+        <v>3.071104380179594</v>
+      </c>
+      <c r="D1789" t="n">
+        <v>1.56216577077868</v>
+      </c>
+      <c r="E1789" t="n">
+        <v>3.695614264177319</v>
+      </c>
+      <c r="F1789" t="n">
+        <v>2.177379683193448</v>
+      </c>
+      <c r="G1789" t="n">
+        <v>4.377532190095664</v>
       </c>
     </row>
   </sheetData>
